--- a/report/test_results_register.xlsx
+++ b/report/test_results_register.xlsx
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 23:00:40</t>
+          <t>2026-05-24 17:15:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14 23:00:50</t>
+          <t>2026-05-24 17:15:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-14 23:00:59</t>
+          <t>2026-05-24 17:15:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-14 23:01:10</t>
+          <t>2026-05-24 17:16:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-14 23:01:19</t>
+          <t>2026-05-24 17:16:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14 23:01:32</t>
+          <t>2026-05-24 17:16:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-14 23:01:44</t>
+          <t>2026-05-24 17:16:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-14 23:01:58</t>
+          <t>2026-05-24 17:16:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-14 23:02:08</t>
+          <t>2026-05-24 17:17:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-14 23:02:20</t>
+          <t>2026-05-24 17:17:10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-14 23:02:30</t>
+          <t>2026-05-24 17:17:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-14 23:02:40</t>
+          <t>2026-05-24 17:17:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-14 23:02:54</t>
+          <t>2026-05-24 17:17:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-14 23:03:06</t>
+          <t>2026-05-24 17:17:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/report/test_results_register.xlsx
+++ b/report/test_results_register.xlsx
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-24 17:15:35</t>
+          <t>2026-05-31 22:10:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-24 17:15:45</t>
+          <t>2026-05-31 22:10:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-24 17:15:56</t>
+          <t>2026-05-31 22:11:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-24 17:16:06</t>
+          <t>2026-05-31 22:11:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-24 17:16:16</t>
+          <t>2026-05-31 22:11:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-24 17:16:27</t>
+          <t>2026-05-31 22:11:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-24 17:16:40</t>
+          <t>2026-05-31 22:12:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-24 17:16:52</t>
+          <t>2026-05-31 22:12:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-24 17:17:01</t>
+          <t>2026-05-31 22:12:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-24 17:17:10</t>
+          <t>2026-05-31 22:13:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-24 17:17:20</t>
+          <t>2026-05-31 22:13:14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-24 17:17:32</t>
+          <t>2026-05-31 22:13:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-24 17:17:43</t>
+          <t>2026-05-31 22:13:38</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-24 17:17:54</t>
+          <t>2026-05-31 22:13:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/report/test_results_register.xlsx
+++ b/report/test_results_register.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-02 16:47:22</t>
+          <t>2026-06-02 17:20:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,6 +501,150 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:20:37</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_registration_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>thuytien1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tien13</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:20:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test_registration_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tien14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:20:55</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_registration_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thuytien9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tien15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:21:05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_registration_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thuytien9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
